--- a/artfynd/A 70466-2021 artfynd.xlsx
+++ b/artfynd/A 70466-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 70466-2021 artfynd.xlsx
+++ b/artfynd/A 70466-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>97668687</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509682.2830227671</v>
+        <v>509682</v>
       </c>
       <c r="R2" t="n">
-        <v>6602949.281468105</v>
+        <v>6602950</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2021-12-22</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-12-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,12 +780,7 @@
         <v>97668688</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509626.5325312954</v>
+        <v>509626</v>
       </c>
       <c r="R3" t="n">
-        <v>6602914.678795789</v>
+        <v>6602915</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,19 +845,9 @@
           <t>2021-12-22</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-12-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,12 +882,7 @@
         <v>97668690</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509625.396708024</v>
+        <v>509625</v>
       </c>
       <c r="R4" t="n">
-        <v>6602763.659181503</v>
+        <v>6602764</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,19 +947,9 @@
           <t>2021-12-22</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-12-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,6 +978,228 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131307669</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vargkloberget, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>509627</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6602915</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>T-Lin-0033</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-12-22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-12-22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131307670</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vargkloberget, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>509682</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6602949</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>T-Lin-0032</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-12-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-12-22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 70466-2021 artfynd.xlsx
+++ b/artfynd/A 70466-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97668687</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97668688</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97668690</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1089,6 +1109,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131307669</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1200,8 +1225,20 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131307670</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>